--- a/Departmental_Ongoing_Works_Professional.xlsx
+++ b/Departmental_Ongoing_Works_Professional.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamil.baig\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamil.baig\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7470" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7470" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -306,9 +306,6 @@
     <t>Purchase Order (PO) issuance</t>
   </si>
   <si>
-    <t>Draft PO under commercial terms review; formal issuance pending.</t>
-  </si>
-  <si>
     <t>Technical Due Diligence</t>
   </si>
   <si>
@@ -318,9 +315,6 @@
     <t>Engineering / Maintenance</t>
   </si>
   <si>
-    <t>Checklist to be formally dispatched to Trützschler following final inputs from FND.</t>
-  </si>
-  <si>
     <t>Consultancy &amp; Design</t>
   </si>
   <si>
@@ -367,6 +361,12 @@
   </si>
   <si>
     <t xml:space="preserve">Cable try work </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft PO under commercial terms review; </t>
+  </si>
+  <si>
+    <t>Checklist to be formally finalized to Trützschler following final inputs from FND.</t>
   </si>
 </sst>
 </file>
@@ -1079,15 +1079,15 @@
       </c>
       <c r="D4" s="3">
         <f>COUNTIF('Fiber Bleaching'!D4:D9, "In Progress")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3">
         <f>COUNTIF('Fiber Bleaching'!D4:D9, "Under Review")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
         <f>COUNTIF('Fiber Bleaching'!D4:D9, "Pending") + COUNTIF('Fiber Bleaching'!D4:D9, "Scheduled")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" s="4">
         <f>C4/B4</f>
@@ -1166,15 +1166,15 @@
       </c>
       <c r="D7" s="6">
         <f>SUM(D4:D6)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7" s="6">
         <f>SUM(E4:E6)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6">
         <f>SUM(F4:F6)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7" s="7">
         <f>C7/B7</f>
@@ -1355,8 +1355,8 @@
       <c r="C5" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>5</v>
+      <c r="D5" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>34</v>
@@ -1415,8 +1415,8 @@
       <c r="C8" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>5</v>
+      <c r="D8" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>43</v>
@@ -1435,8 +1435,8 @@
       <c r="C9" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>6</v>
+      <c r="D9" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>47</v>
@@ -1632,7 +1632,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>74</v>
@@ -1789,7 +1789,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="28.5">
+    <row r="7" spans="1:6">
       <c r="A7" s="17">
         <v>4</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>39</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.5">
@@ -1814,19 +1814,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>95</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>96</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.5">
@@ -1834,19 +1834,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.5">
@@ -1854,19 +1854,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.5">
@@ -1874,19 +1874,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.5">
@@ -1894,19 +1894,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
